--- a/docs/analysis/2026-08-09-gap-review2.xlsx
+++ b/docs/analysis/2026-08-09-gap-review2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="검토2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토2'!$A$4:$K$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토2'!$A$4:$K$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>합성지(30m)-아누코</t>
+          <t>채널용 입체바</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>127폭</t>
+          <t>금색/100mm*3m</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -615,25 +615,25 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAP-P127</t>
+          <t>SGM-IPB100-GD</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>합성지-프라임 127폭 / 127폭</t>
+          <t>입체바 1.0T 100mm 금색 / 100mm</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAPGR-P127</t>
+          <t>SK-2146</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>JG-WBOARD</t>
+          <t>SK-2145</t>
         </is>
       </c>
     </row>
@@ -646,17 +646,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>합성지(30m)-아누코</t>
+          <t>채널용 입체바</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>152폭</t>
+          <t>녹색/100mm*3m</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -666,25 +666,25 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAP-P152</t>
+          <t>SGM-IPB100-GN</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>합성지-프라임 152폭 / 152폭</t>
+          <t>입체바 1.0T 100mm 녹색 / 100mm</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAPGR-P152</t>
+          <t>SK-2146</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>HJ-UVEMB-P152</t>
+          <t>SK-2145</t>
         </is>
       </c>
     </row>
@@ -697,17 +697,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>합성지(30m)-아누코</t>
+          <t>채널용 입체바</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>60폭</t>
+          <t>밤색/100mm*3m</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -717,25 +717,25 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAP-P60</t>
+          <t>SGM-IPB100-BR</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>합성지-프라임 60폭 / 60폭</t>
+          <t>입체바 1.0T 100mm 밤색 / 100mm</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAPGR-P60</t>
+          <t>SK-2146</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>JG-E26T-P60</t>
+          <t>SK-2145</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>합성지(30m)-아누코</t>
+          <t>채널용 입체바</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>90폭</t>
+          <t>연두/100mm*3m</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -768,710 +768,740 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAP-P90</t>
+          <t>SGM-IPB100-YG</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>합성지-프라임 90폭 / 90폭</t>
+          <t>입체바 1.0T 100mm 연두 / 100mm</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>PJ-HAPGR-P90</t>
+          <t>SK-2146</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>TPL-090</t>
+          <t>SK-2145</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>SPM013G</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>105폭</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>SPM011G-105</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>일반시트 SPM011G / 105cm</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>SPM022G-105</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>SPC031G-105</t>
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>연청색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LB</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 연청색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-NB</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>SPM013G</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>127폭</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>SPM011G-127</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>일반시트 SPM011G / 127cm</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>JG-WBOARD</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>HJ-YMSIDE-P127</t>
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>연핑크/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LP</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 연핑크 / 100mm</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-DP</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>SPM013G</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>137폭</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>SPM011G-137</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>일반시트 SPM011G / 137cm</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>SPM022G-137</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>SPT031M</t>
+      <c r="A11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>연회색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LG</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 연회색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-DG</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>무광 솔벤 PVC(켈)-50m</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>152폭</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>PJ-KEL-P152</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>PVC(켈)-프라임 152폭 / 152폭</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>JG-E4-P152</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>JG-NJ4-P152</t>
+      <c r="A12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>적색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-RD</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 적색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>SK-1148</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>무광 솔벤 PVC(켈)-50m</t>
+          <t>채널용 입체바</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>152폭</t>
+          <t>주황색/100mm*3m</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>실적단가 있음</t>
+          <t>단가 없음</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>PJ-KEL-P152</t>
+          <t>SGM-IPB100-OR</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>PVC(켈)-프라임 152폭 / 152폭</t>
+          <t>입체바 1.0T 100mm 주황색 / 100mm</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>JG-E4-P152</t>
+          <t>SGM-IPB100-YL</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>JG-NJ4-P152</t>
+          <t>SK-2146</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>진청색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-NB</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 진청색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LB</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>진핑크/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-DP</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 진핑크 / 100mm</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LP</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>진회색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-DG</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 진회색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-LG</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>채널용 입체바</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>황색/100mm*3m</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-YL</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>입체바 1.0T 100mm 황색 / 100mm</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>SGM-IPB100-OR</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>SK-2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SPM013G</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>105폭</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>SPM011G-105</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>일반시트 SPM011G / 105cm</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>SPM022G-105</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>SPC031G-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>SPM013G</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>127폭</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>SPM011G-127</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>일반시트 SPM011G / 127cm</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>JG-WBOARD</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>HJ-YMSIDE-P127</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>SPM013G</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>137폭</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>SPM011G-137</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>일반시트 SPM011G / 137cm</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>SPM022G-137</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>SPT031M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>무광 솔벤 PVC(켈)-50m</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>90폭</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>152폭</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>PJ-KEL-P90</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PVC(켈)-프라임 90폭 / 90폭</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>PJ-KEL-P152</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>PVC(켈)-프라임 152폭 / 152폭</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>JG-E4-P90</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>JG-NJ4-P90</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>아크릴 2T</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>[제품]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>UV-ACR-2T-W</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>UV 아크릴 2T 백색 / 2T 백색</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>UV-ACR-2T-B</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>UV-ACR-2T-C</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>아크릴 3T</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>[제품]</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-3T-W</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UV 아크릴 3T 백색 / 3T 백색</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-3T-B</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-3T-C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>아크릴 5T</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>[제품]</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-5T-W</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UV 아크릴 5T 백색 / 5T 백색</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-5T-B</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>UV-ACR-5T-C</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>무광 솔벤 PVC(켈)그레이-50m</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>105폭</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>JG-E4-P152</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>JG-NJ4-P152</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>무광 솔벤 PVC(켈)-50m</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>152폭</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>SPM022G-105</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>그레이시트 SPM022G / 105cm</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>AQ-KELG</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>SV-SHEETG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>무광 솔벤 PVC(켈)그레이-50m</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>137폭</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>SPM022G-137</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>그레이시트 SPM022G / 137cm</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>SVM-137</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>SVAT-137</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>백릿(30m)-아누코</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>127폭</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>PJ-BACKLIT-P127</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>수성 백릿-프라임 127폭 / 127폭</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="n">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>PJ-KEL-P152</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>PVC(켈)-프라임 152폭 / 152폭</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>JG-WBOARD</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HJ-YMSIDE-P127</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>백릿(30m)-아누코</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>90폭</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>PJ-BACKLIT-P90</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>수성 백릿-프라임 90폭 / 90폭</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>TPL-090</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>HJ-YMSIDE-P90</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>백릿(30m)-잉크테크</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>127폭</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>PJ-BACKLIT-P127</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>수성 백릿-프라임 127폭 / 127폭</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>KEL-IT-127</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>SYN-IT-127</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>JG-E4-P152</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>JG-NJ4-P152</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>백릿(30m)-잉크테크</t>
+          <t>무광 솔벤 PVC(켈)-50m</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1486,17 +1516,17 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>단가 없음</t>
+          <t>실적단가 있음</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>PJ-BACKLIT-P90</t>
+          <t>PJ-KEL-P90</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>수성 백릿-프라임 90폭 / 90폭</t>
+          <t>PVC(켈)-프라임 90폭 / 90폭</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -1504,29 +1534,29 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>KEL-IT-090</t>
+          <t>JG-E4-P90</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>KELG-IT-090</t>
+          <t>JG-NJ4-P90</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>스카시30T</t>
+          <t>아크릴 2T</t>
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[제품]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1536,12 +1566,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>UV-SKS-30T-W</t>
+          <t>UV-ACR-2T-W</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>UV 스카시 30T 백색 / 30T 백색</t>
+          <t>UV 아크릴 2T 백색 / 2T 백색</t>
         </is>
       </c>
       <c r="I24" s="6" t="n">
@@ -1549,29 +1579,29 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>UV-SKS-30T-B</t>
+          <t>UV-ACR-2T-B</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>SKS-30T-W-36</t>
+          <t>UV-ACR-2T-C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>스카시50T</t>
+          <t>아크릴 3T</t>
         </is>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[제품]</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1581,12 +1611,12 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>SKS-50T-W-36</t>
+          <t>UV-ACR-3T-W</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>스카시 / 50T 백색 3x6</t>
+          <t>UV 아크릴 3T 백색 / 3T 백색</t>
         </is>
       </c>
       <c r="I25" s="8" t="n">
@@ -1594,371 +1624,367 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>SIGN-SCS</t>
+          <t>UV-ACR-3T-B</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>SGM-FOOT-F500</t>
+          <t>UV-ACR-3T-C</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>유광 솔벤 PVC(켈)-50m</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>아크릴 5T</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>[제품]</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>UV-ACR-5T-W</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>UV 아크릴 5T 백색 / 5T 백색</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>UV-ACR-5T-B</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>UV-ACR-5T-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>LC6771M</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>122폭/50m</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>SK-1887</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>[중단] LG시트-LC6772-(122폭)</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>LC6770P</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>LT4071M</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>LC6781M</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>122폭/50m</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>SK-1887</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>[중단] LG시트-LC6772-(122폭)</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>LC6770P</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SK-1619</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>무광 솔벤 PVC(켈)그레이-50m</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>105폭</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>실적단가 있음</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>SPM022G-105</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>그레이시트 SPM022G / 105cm</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>PJ-KELGR</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>AQ-KELG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>무광 솔벤 PVC(켈)그레이-50m</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>137폭</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>실적단가 있음</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>SPM022G-137</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>그레이시트 SPM022G / 137cm</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>PJ-KELGR</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>SVM-137</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>백릿(30m)-잉크테크</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>127폭</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>JG-E26T-P127</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>E26T 유광(45m/200g) 127폭 / 127폭</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="n">
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>PJ-BACKLIT-P127</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>수성 백릿-프라임 127폭 / 127폭</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>PJ-KEL-P127</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>PJ-KELGR-P127</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>유광 솔벤 PVC(켈)-50m</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>KEL-IT-127</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>SYN-IT-127</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>백릿(30m)-잉크테크</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>90폭</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>JG-E26T-P90</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>E26T 유광(45m/200g) 90폭 / 90폭</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>PJ-BACKLIT-P90</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>수성 백릿-프라임 90폭 / 90폭</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>PJ-KEL-P90</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>PJ-KELGR-P90</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>유광 솔벤 PVC(켈)그레이-50m</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>105폭</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>SPM022G-105</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>그레이시트 SPM022G / 105cm</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>AQ-KELG</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>SV-SHEETG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>유광 솔벤 PVC(켈)그레이-50m</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>137폭</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>실적단가 있음</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>SPM022G-137</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>그레이시트 SPM022G / 137cm</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>SVM-137</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>SVAT-137</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>LC6771M</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>122폭/50m</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>LC6770P</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>조명시트 LC6770P / 122폭/50m</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>LT4071M</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>LT4080M</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr"/>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>LM54000(보급형)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>137폭</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>LM5400-137</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>조명시트 LM5400 / 137폭</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>SPT031M</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>LW2800M</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>3M시트-IJ1210C-10</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>137폭/50m</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>[상품]</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>IJ35C-137</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>3M IJ35C-10 / 137폭/50m</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>LM5400-137</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>SPT031M</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>KEL-IT-090</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>KELG-IT-090</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B33" s="7" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>3M시트-IJ1210G-10</t>
+          <t>유광 솔벤 PVC(켈)-50m</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>127폭/50m/회색</t>
+          <t>127폭</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1968,25 +1994,25 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>단가 없음</t>
+          <t>실적단가 있음</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>SPM022G-127</t>
+          <t>JG-E26T-P127</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>그레이시트 SPM022G / 127cm</t>
+          <t>E26T 유광(45m/200g) 127폭 / 127폭</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>PJ-HAPGR-P127</t>
+          <t>PJ-KEL-P127</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -1996,166 +2022,170 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>TS전용 싱글아일렛(자동몰드)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>12파이(24호)/은색</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>[제품]</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>ACC-MOLD-24</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>자동몰드 24호 / 24호·12파이</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="n">
+      <c r="A34" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>유광 솔벤 PVC(켈)-50m</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>90폭</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>실적단가 있음</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>JG-E26T-P90</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>E26T 유광(45m/200g) 90폭 / 90폭</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>ACC-045-12P-S</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>ACC-045-24-S</t>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>PJ-KEL-P90</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>PJ-KELGR-P90</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>16</v>
+      <c r="A35" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>UV 투명패트 비점착(188)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>127폭/30m</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>유광 솔벤 PVC(켈)그레이-50m</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>105폭</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>실적단가 있음</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>UV-PATC</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>UV 투명패트</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="n">
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>SPM022G-105</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>그레이시트 SPM022G / 105cm</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n">
         <v>0.46</v>
       </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>SPC031G-127</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>HJ-UVEMB-P127</t>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>PJ-KELGR</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>AQ-KELG</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr"/>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>각목</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>100폭</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="A36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>유광 솔벤 PVC(켈)그레이-50m</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>137폭</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>[상품]</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>단가 없음</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>RM-DOAN-100</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>도안지 / 100폭</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>SK-26797</t>
-        </is>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>SK-2833</t>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>실적단가 있음</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>SPM022G-137</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>그레이시트 SPM022G / 137cm</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>PJ-KELGR</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>SVM-137</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B37" s="7" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>간판채널</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n"/>
+          <t>LC6750G</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>122폭/50m</t>
+        </is>
+      </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>[제품]</t>
+          <t>[상품]</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -2165,41 +2195,41 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>SIGN-CH</t>
+          <t>SK-1887</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>채널간판</t>
+          <t>[중단] LG시트-LC6772-(122폭)</t>
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>SIGN-PRT</t>
+          <t>LC6770P</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>SGM-CRF</t>
+          <t>SK-1619</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B38" s="7" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>고무자석시트-일반(0.6T)</t>
+          <t>LM54000(보급형)</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>100폭/10m</t>
+          <t>137폭</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2214,41 +2244,41 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>MAG-100</t>
+          <t>LM5400-137</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>고무자석시트 / 100cm</t>
+          <t>조명시트 LM5400 / 137폭</t>
         </is>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>RM-DOAN-100</t>
+          <t>SPT031M</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>ULTRA-CAL-100</t>
+          <t>LW2800M</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B39" s="7" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>고무자석시트-차량용(0.6T)</t>
+          <t>3M시트-IJ1210C-10</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>60폭</t>
+          <t>137폭/50m</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2263,42 +2293,46 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>MAG-060</t>
+          <t>IJ35C-137</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>고무자석시트 / 60cm</t>
+          <t>3M IJ35C-10 / 137폭/50m</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>JG-E2-P60</t>
+          <t>LM5400-137</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>HJ-MGILBO-P60</t>
+          <t>SPT031M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B40" s="7" t="inlineStr"/>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>돼지표본드</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n"/>
+          <t>3M시트-IJ1210G-10</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>127폭/50m/회색</t>
+        </is>
+      </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>[원재료]</t>
+          <t>[상품]</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2308,48 +2342,46 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>SGM-PBOND</t>
+          <t>SPM022G-127</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>돼지표본드 / 3kg</t>
+          <t>그레이시트 SPM022G / 127cm</t>
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>SGM-BOND</t>
+          <t>PJ-HAPGR-P127</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>SK-375</t>
+          <t>PJ-KELGR-P127</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>무광 코팅지 자동용(61m/140g)-코인텍</t>
+          <t>TS전용 싱글아일렛(자동몰드)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>127폭</t>
+          <t>12파이(24호)/은색</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[제품]</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2359,41 +2391,43 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>JG-JD61-P127</t>
+          <t>ACC-MOLD-24</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>자동용 코팅지 엠보(61m/120g) 127폭 / 127폭</t>
+          <t>자동몰드 24호 / 24호·12파이</t>
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>HJ-MGAUTO-P127</t>
+          <t>ACC-045-12P-S</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>MCN200-CO-127</t>
+          <t>ACC-045-24-S</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>솔벤 텐트천(300D)</t>
+          <t>UV 투명패트 비점착(188)</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>160폭</t>
+          <t>127폭/30m</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2403,44 +2437,48 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>단가 없음</t>
+          <t>실적단가 있음</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>SVT-160</t>
+          <t>PAT-UVC50-127</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>솔벤 텐트천 / 160cm</t>
+          <t>UV투명 패트배너 50M / 127cm</t>
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>SVM-160</t>
+          <t>UV-PATC</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>SK-26802</t>
+          <t>SPC031G-127</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>알마이트3T</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="n"/>
+          <t>각목</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>100폭</t>
+        </is>
+      </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -2453,43 +2491,39 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>ALM-3T-S-48</t>
+          <t>RM-DOAN-100</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>알마이트 / 3T 은색 4x8</t>
+          <t>도안지 / 100폭</t>
         </is>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>TAPE-3T</t>
+          <t>SK-1618</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>UV-FMX-3T-W</t>
+          <t>SK-26797</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B44" s="7" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>울트라 칼라시트-(내부용)</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>100폭/검정/무광</t>
-        </is>
-      </c>
+          <t>간판</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -2502,12 +2536,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>ULTRA-CAL-100</t>
+          <t>SGM-BOARD</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>울트라 칼라시트 / 100cm</t>
+          <t>[중단] 간판 후판</t>
         </is>
       </c>
       <c r="I44" s="9" t="n">
@@ -2515,33 +2549,29 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>ULTRA-BOJO-100</t>
+          <t>SGM-BOARD-B90</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>RM-DOAN-100</t>
+          <t>SGM-BOARD-B100</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B45" s="7" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>윈드배너 부품-크로스베스</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>6t/4kg</t>
-        </is>
-      </c>
+          <t>간판채널</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[제품]</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -2551,42 +2581,46 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>ACC-016</t>
+          <t>SIGN-CH</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>윈드배너 부품(크로스/베이스)</t>
+          <t>채널간판</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>JJN-06T</t>
+          <t>SGM-BOARD</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>ACC-017</t>
+          <t>SIGN-PRT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B46" s="7" t="inlineStr"/>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>자이언트배너 출력</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n"/>
+          <t>고무자석시트-일반(0.6T)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>100폭/10m</t>
+        </is>
+      </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>[제품]</t>
+          <t>[상품]</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -2596,39 +2630,43 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>ACC-023</t>
+          <t>MAG-100</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>자이언트배너 폴세트</t>
+          <t>고무자석시트 / 100cm</t>
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>TRGI-PO</t>
+          <t>SK-1618</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>TRGI-ME</t>
+          <t>RM-DOAN-100</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B47" s="7" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>철제배너 부속SET-TSO</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n"/>
+          <t>고무자석시트-차량용(0.6T)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>60폭</t>
+        </is>
+      </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
           <t>[상품]</t>
@@ -2641,46 +2679,42 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>ACC-027</t>
+          <t>MAG-060</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>실외 철제배너 물통SET(TSO)</t>
+          <t>고무자석시트 / 60cm</t>
         </is>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>ACC-026</t>
+          <t>JG-E2-P60</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>ACC-028</t>
+          <t>HJ-MGILBO-P60</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B48" s="7" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>포맥스-국산</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>4*8(10T)</t>
-        </is>
-      </c>
+          <t>돼지표본드</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>[상품]</t>
+          <t>[원재료]</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -2690,46 +2724,46 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>SK-2824</t>
+          <t>SGM-PBOND</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>예스포맥스10T4*8백색</t>
+          <t>돼지표본드 / 3kg</t>
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>SK-2258</t>
+          <t>SK-414</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>UV-FMX-10T-W</t>
+          <t>SGM-BOND</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B49" s="7" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>후판</t>
+          <t>솔벤 텐트천(300D)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>200cm</t>
+          <t>160폭</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>[원재료]</t>
+          <t>[상품]</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -2739,12 +2773,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>SVM-200</t>
+          <t>SVT-160</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>솔벤 매쉬 / 200cm</t>
+          <t>솔벤 텐트천 / 160cm</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
@@ -2752,17 +2786,299 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
+          <t>SVM-160</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>SK-26802</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr"/>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>알마이트3T</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>ALM-3T-S-48</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>알마이트 / 3T 은색 4x8</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>TAPE-3T</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>UV-FMX-3T-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>울트라 칼라시트-(내부용)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>100폭/검정/무광</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>ULTRA-CAL-100</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>울트라 칼라시트 / 100cm</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>ULTRA-BOJO-100</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>RM-DOAN-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>윈드배너 부품-크로스베스</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>6t/4kg</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>ACC-016</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>윈드배너 부품(크로스/베이스)</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>JJN-06T</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>ACC-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr"/>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>자이언트배너 출력</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>[제품]</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>ACC-023</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>자이언트배너 폴세트</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>TRGI-PO</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>TRGI-ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr"/>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>철제배너 부속SET-TSO</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>[상품]</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>ACC-027</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>실외 철제배너 물통SET(TSO)</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>ACC-026</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>ACC-028</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>후판</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>200cm</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>[원재료]</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>단가 없음</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>SVM-200</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>솔벤 매쉬 / 200cm</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
           <t>SVB-200</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K55" s="6" t="inlineStr">
         <is>
           <t>SVT-200</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K49"/>
+  <autoFilter ref="A4:K55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>